--- a/public/export/declaration_list/declaration_tmp.xlsx
+++ b/public/export/declaration_list/declaration_tmp.xlsx
@@ -10,7 +10,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="2jjV85mzFAS8mcAlzMrEWA6PUwxG7lwfDHxwQvvLK4A="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="troV2rKY6PoK2S6VOBP3qOMk7sAuBIC/rTUhPqxHYfY="/>
     </ext>
   </extLst>
 </workbook>
@@ -63,7 +63,7 @@
       <rPr>
         <rFont val="Times New Roman"/>
         <color rgb="FF000000"/>
-        <sz val="11.0"/>
+        <sz val="12.0"/>
       </rPr>
       <t>(Dùng cho công dân Việt Nam xuất nhập cảnh sang các thành phố biên giới của Trung Quốc tiếp giáp Việt Nam)</t>
     </r>
@@ -184,23 +184,13 @@
         <sz val="12.0"/>
       </rPr>
       <t xml:space="preserve">Xác nhận của Công an
-</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <b/>
-        <color rgb="FF000000"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve">xã, phường, thị trấn nơi cư trú </t>
+xã, phường, thị trấn nơi cư trú </t>
     </r>
     <r>
       <rPr>
         <rFont val="Times New Roman"/>
         <color rgb="FF000000"/>
         <sz val="12.0"/>
-        <vertAlign val="superscript"/>
       </rPr>
       <t xml:space="preserve">(3)
 </t>
@@ -416,7 +406,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border/>
     <border>
       <left style="thin">
@@ -483,16 +473,11 @@
       <top/>
       <bottom/>
     </border>
-    <border>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -547,7 +532,6 @@
       <alignment horizontal="left" readingOrder="1" shrinkToFit="1" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="1" shrinkToFit="1" vertical="center" wrapText="0"/>
     </xf>
@@ -582,7 +566,7 @@
       <alignment horizontal="left" readingOrder="1" shrinkToFit="1" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="1" vertical="top" wrapText="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="1" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="1" shrinkToFit="1" vertical="top" wrapText="0"/>
@@ -829,7 +813,7 @@
     <col customWidth="1" min="19" max="19" width="4.0"/>
     <col customWidth="1" min="20" max="20" width="4.43"/>
     <col customWidth="1" min="21" max="21" width="4.29"/>
-    <col customWidth="1" min="22" max="22" width="0.71"/>
+    <col customWidth="1" min="22" max="22" width="2.43"/>
     <col customWidth="1" min="23" max="26" width="8.71"/>
   </cols>
   <sheetData>
@@ -1008,20 +992,20 @@
         <v>8</v>
       </c>
       <c r="C9" s="21"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
       <c r="G9" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I9" s="23"/>
+      <c r="I9" s="22"/>
       <c r="K9" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="L9" s="23"/>
+      <c r="L9" s="22"/>
       <c r="N9" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="23"/>
+      <c r="R9" s="22"/>
       <c r="W9" s="10"/>
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
@@ -1059,22 +1043,22 @@
       <c r="C11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="24"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="25"/>
+      <c r="H11" s="24"/>
       <c r="I11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="26"/>
+      <c r="J11" s="25"/>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="S11" s="26"/>
+      <c r="S11" s="25"/>
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
@@ -1085,16 +1069,16 @@
       <c r="B12" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="26"/>
+      <c r="E12" s="25"/>
       <c r="H12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="26"/>
+      <c r="K12" s="25"/>
       <c r="N12" s="17"/>
       <c r="O12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="S12" s="27" t="s">
+      <c r="S12" s="26" t="s">
         <v>19</v>
       </c>
       <c r="W12" s="10"/>
@@ -1107,13 +1091,13 @@
       <c r="B13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="27" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="29"/>
+      <c r="J13" s="28"/>
       <c r="K13" s="17" t="s">
         <v>23</v>
       </c>
@@ -1122,7 +1106,7 @@
       <c r="O13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="S13" s="30"/>
+      <c r="S13" s="29"/>
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
@@ -1134,15 +1118,15 @@
       <c r="C14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="30"/>
+      <c r="F14" s="29"/>
       <c r="I14" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="31"/>
+      <c r="L14" s="30"/>
       <c r="O14" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="S14" s="26"/>
+      <c r="S14" s="25"/>
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
@@ -1153,13 +1137,13 @@
       <c r="B15" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="31" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="S15" s="33" t="s">
+      <c r="S15" s="32" t="s">
         <v>31</v>
       </c>
       <c r="W15" s="10"/>
@@ -1169,7 +1153,7 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="10"/>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="32" t="s">
         <v>32</v>
       </c>
       <c r="W16" s="10"/>
@@ -1182,7 +1166,7 @@
       <c r="B17" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="31" t="s">
         <v>34</v>
       </c>
       <c r="W17" s="10"/>
@@ -1195,7 +1179,7 @@
       <c r="B18" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="K18" s="33" t="s">
+      <c r="K18" s="32" t="s">
         <v>36</v>
       </c>
       <c r="W18" s="10"/>
@@ -1205,7 +1189,7 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="10"/>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="32" t="s">
         <v>37</v>
       </c>
       <c r="W19" s="10"/>
@@ -1253,11 +1237,11 @@
     </row>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="33" t="s">
         <v>39</v>
       </c>
       <c r="K22" s="10"/>
-      <c r="L22" s="35" t="s">
+      <c r="L22" s="34" t="s">
         <v>40</v>
       </c>
       <c r="V22" s="10"/>
@@ -1361,7 +1345,7 @@
       <c r="I28" s="10"/>
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
-      <c r="L28" s="36"/>
+      <c r="L28" s="35"/>
       <c r="V28" s="10"/>
       <c r="W28" s="10"/>
       <c r="X28" s="10"/>
@@ -1398,7 +1382,7 @@
     </row>
     <row r="30" ht="56.25" customHeight="1">
       <c r="A30" s="10"/>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="36" t="s">
         <v>41</v>
       </c>
       <c r="V30" s="10"/>
@@ -7851,7 +7835,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="49.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>42</v>
       </c>
     </row>
